--- a/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital De Patrimonio Cultural.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital De Patrimonio Cultural.xlsx
@@ -426,13 +426,13 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>no</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -666,7 +666,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -734,6 +734,9 @@
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -5744,7 +5747,7 @@
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
-      <c r="I18" s="23" t="s">
+      <c r="I18" s="24" t="s">
         <v>132</v>
       </c>
       <c r="J18" s="6"/>
@@ -5776,7 +5779,7 @@
       <c r="C19" s="11">
         <v>18.0</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>133</v>
       </c>
       <c r="E19" s="10"/>
@@ -8096,7 +8099,7 @@
       <c r="K2" s="20">
         <v>1.0</v>
       </c>
-      <c r="L2" s="24"/>
+      <c r="L2" s="25"/>
       <c r="M2" s="20">
         <v>1.0</v>
       </c>
@@ -8112,10 +8115,10 @@
       <c r="S2" s="17"/>
     </row>
     <row r="3" ht="126.75" customHeight="1">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="25"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="11">
         <v>2.0</v>
       </c>
@@ -8125,33 +8128,33 @@
       <c r="E3" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25" t="s">
+      <c r="F3" s="26"/>
+      <c r="G3" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="J3" s="25"/>
+      <c r="J3" s="26"/>
       <c r="K3" s="19">
         <v>5.0</v>
       </c>
-      <c r="L3" s="26"/>
+      <c r="L3" s="27"/>
       <c r="M3" s="19">
         <v>5.0</v>
       </c>
-      <c r="N3" s="25"/>
+      <c r="N3" s="26"/>
       <c r="O3" s="19">
         <v>1.0</v>
       </c>
-      <c r="P3" s="25"/>
+      <c r="P3" s="26"/>
       <c r="Q3" s="19">
         <v>3.0</v>
       </c>
-      <c r="R3" s="25"/>
+      <c r="R3" s="26"/>
       <c r="S3" s="19">
         <v>4.0</v>
       </c>
@@ -8177,26 +8180,26 @@
       <c r="H4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="28" t="s">
         <v>152</v>
       </c>
       <c r="J4" s="17"/>
       <c r="K4" s="19">
         <v>5.0</v>
       </c>
-      <c r="L4" s="26"/>
+      <c r="L4" s="27"/>
       <c r="M4" s="19">
         <v>5.0</v>
       </c>
-      <c r="N4" s="25"/>
+      <c r="N4" s="26"/>
       <c r="O4" s="19">
         <v>1.0</v>
       </c>
-      <c r="P4" s="25"/>
+      <c r="P4" s="26"/>
       <c r="Q4" s="19">
         <v>3.0</v>
       </c>
-      <c r="R4" s="25"/>
+      <c r="R4" s="26"/>
       <c r="S4" s="19">
         <v>4.0</v>
       </c>
@@ -8231,7 +8234,7 @@
       <c r="K5" s="20">
         <v>1.0</v>
       </c>
-      <c r="L5" s="24"/>
+      <c r="L5" s="25"/>
       <c r="M5" s="20">
         <v>1.0</v>
       </c>
@@ -8251,10 +8254,10 @@
       </c>
     </row>
     <row r="6" ht="126.75" customHeight="1">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="25"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="11">
         <v>5.0</v>
       </c>
@@ -8264,44 +8267,44 @@
       <c r="E6" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="J6" s="25"/>
+      <c r="J6" s="26"/>
       <c r="K6" s="19">
         <v>3.0</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="19">
         <v>3.0</v>
       </c>
-      <c r="N6" s="25"/>
+      <c r="N6" s="26"/>
       <c r="O6" s="19">
         <v>5.0</v>
       </c>
-      <c r="P6" s="25"/>
+      <c r="P6" s="26"/>
       <c r="Q6" s="19">
         <v>4.0</v>
       </c>
-      <c r="R6" s="25"/>
+      <c r="R6" s="26"/>
       <c r="S6" s="19">
         <v>3.0</v>
       </c>
     </row>
     <row r="7" ht="126.75" customHeight="1">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="26"/>
       <c r="C7" s="11">
         <v>5.0</v>
       </c>
@@ -8311,33 +8314,33 @@
       <c r="E7" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25" t="s">
+      <c r="F7" s="26"/>
+      <c r="G7" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="J7" s="25"/>
+      <c r="J7" s="26"/>
       <c r="K7" s="19">
         <v>3.0</v>
       </c>
-      <c r="L7" s="26"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="19">
         <v>3.0</v>
       </c>
-      <c r="N7" s="25"/>
+      <c r="N7" s="26"/>
       <c r="O7" s="19">
         <v>5.0</v>
       </c>
-      <c r="P7" s="25"/>
+      <c r="P7" s="26"/>
       <c r="Q7" s="19">
         <v>4.0</v>
       </c>
-      <c r="R7" s="25"/>
+      <c r="R7" s="26"/>
       <c r="S7" s="19">
         <v>3.0</v>
       </c>
@@ -8372,7 +8375,7 @@
       <c r="K8" s="20">
         <v>1.0</v>
       </c>
-      <c r="L8" s="24"/>
+      <c r="L8" s="25"/>
       <c r="M8" s="20">
         <v>1.0</v>
       </c>
@@ -8421,7 +8424,7 @@
       <c r="K9" s="20">
         <v>1.0</v>
       </c>
-      <c r="L9" s="24"/>
+      <c r="L9" s="25"/>
       <c r="M9" s="20">
         <v>1.0</v>
       </c>
